--- a/docs/swift/data/field/erosion_field_survey.xlsx
+++ b/docs/swift/data/field/erosion_field_survey.xlsx
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026101013</t>
+          <t>2026101018</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/swift/data/field/erosion_field_survey.xlsx
+++ b/docs/swift/data/field/erosion_field_survey.xlsx
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026101018</t>
+          <t>2026101209</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/swift/data/field/erosion_field_survey.xlsx
+++ b/docs/swift/data/field/erosion_field_survey.xlsx
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026101209</t>
+          <t>2026101216</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/swift/data/field/erosion_field_survey.xlsx
+++ b/docs/swift/data/field/erosion_field_survey.xlsx
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026101216</t>
+          <t>2026101914</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/swift/data/field/erosion_field_survey.xlsx
+++ b/docs/swift/data/field/erosion_field_survey.xlsx
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026101914</t>
+          <t>2026102613</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
